--- a/temp/MACRO_ACCOUNT_20250207.xlsx
+++ b/temp/MACRO_ACCOUNT_20250207.xlsx
@@ -471,8 +471,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-15.7</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-15,7</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -496,8 +498,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>15.7</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>15,7</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -521,8 +525,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>-61314.58</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-61314,58</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -546,8 +552,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>-1952341.38</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-1952341,38</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -571,8 +579,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>-33305.66</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-33305,66</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -596,8 +606,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>2046961.62</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2046961,62</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -621,8 +633,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>-26100</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-26100,0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -646,8 +660,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>-5481</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-5481,0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -671,8 +687,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>31581</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>31581,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -696,8 +714,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>-0.7</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0,7</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -721,8 +741,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0.7</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -746,8 +768,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>-34894.91</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-34894,91</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -771,8 +795,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>-31494.25</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-31494,25</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -796,8 +822,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>-1011305.27</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-1011305,27</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -821,8 +849,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1077694.43</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1077694,43</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -846,8 +876,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>-26100</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-26100,0</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -871,8 +903,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>-5481</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-5481,0</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -896,8 +930,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>31581</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>31581,0</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -921,8 +957,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>-0.12</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -946,8 +984,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0.12</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -971,8 +1011,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>-5655.61</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-5655,61</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -996,8 +1038,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>-31384.09</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-31384,09</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1021,8 +1065,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>-32990</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-32990,0</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1046,8 +1092,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>70029.7</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>70029,7</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1071,8 +1119,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>-26100</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-26100,0</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1096,8 +1146,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>-5481</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-5481,0</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1121,8 +1173,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>31581</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>31581,0</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1146,8 +1200,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>-0.67</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-0,67</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1171,8 +1227,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0.67</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0,67</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1196,8 +1254,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>-3578.02</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-3578,02</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1221,8 +1281,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>-30262.45</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>-30262,45</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1246,8 +1308,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>-89004.8</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>-89004,8</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1271,8 +1335,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>122845.27</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>122845,27</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1296,8 +1362,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>-24180</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-24180,0</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1321,8 +1389,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>-5077.8</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-5077,8</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1346,8 +1416,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>29257.8</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>29257,8</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
